--- a/naver-place-crawler/results_health/인천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/인천_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>테이스트피트니스헬스&amp;PT24시 인천호구포역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>tastehgp@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1313-9022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 남동구 호구포로 212 4층 401호 402호, 403호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>http://pf.kakao.com/_exmwzX</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a1vf2</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>647</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="n">
-        <v>849</v>
+        <v>21</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>69</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>2089899080</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/2089899080</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>랩스휘트니스 헬스 PT 계산역점</t>
+          <t>머슬몽키짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rapsgs05@naver.com</t>
+          <t>coke3183@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1303-2584</t>
+          <t>0507-1407-9979</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 경명대로 1048 동성빌딩 B1층 랩스휘트니스 계산역점</t>
+          <t>인천 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/muscle_monkey_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d6xd</t>
+          <t>https://talk.naver.com/ct/w4btcu</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2726</v>
+        <v>234</v>
       </c>
       <c r="Q3" t="n">
-        <v>2727</v>
+        <v>147</v>
       </c>
       <c r="R3" t="n">
-        <v>5453</v>
+        <v>381</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>37060444</t>
+          <t>38234040</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37060444</t>
+          <t>https://m.place.naver.com/place/38234040</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머슬프로짐 PT 헬스</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rkdals5404@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1445-7902</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 641 근영프라자 2층, 머슬프로짐</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1511</v>
+        <v>656</v>
       </c>
       <c r="Q4" t="n">
-        <v>1511</v>
+        <v>859</v>
       </c>
       <c r="R4" t="n">
-        <v>3022</v>
+        <v>1515</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,24 +836,24 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>142646646</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/142646646</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -855,7 +863,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -867,12 +875,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -911,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="R5" t="n">
-        <v>1924</v>
+        <v>2842</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,41 +944,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>휘트니스칸 헬스&amp;PT&amp;골프&amp;요가&amp;필라테스 마전점</t>
+          <t>올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kann004@naver.com</t>
+          <t>all_night_b@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1365-4330</t>
+          <t>0507-1334-5596</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 완정로 70 영남탑스빌아파트 상가 401호</t>
+          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>https://www.instagram.com/all.night_official</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wssak29</t>
+          <t>https://talk.naver.com/ct/w41wqc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>669</v>
+        <v>1308</v>
       </c>
       <c r="Q6" t="n">
-        <v>664</v>
+        <v>920</v>
       </c>
       <c r="R6" t="n">
-        <v>1333</v>
+        <v>2228</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,56 +1032,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1220498447</t>
+          <t>1342318850</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220498447</t>
+          <t>https://m.place.naver.com/place/1342318850</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디소나타 헬스 PT 청라</t>
+          <t>매드볼릭 PT 헬스장 송도</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>body_sonata@naver.com</t>
+          <t>madbolic-songdo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1404-7217</t>
+          <t>0507-1352-6741</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 서구 중봉대로586번길 15 청연프라자 10층</t>
+          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://2080ttt.wixsite.com/bodysonata</t>
+          <t>https://blog.naver.com/madbolic-songdo</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1093,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc46ox</t>
+          <t>https://talk.naver.com/ct/w46104</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1548</v>
+        <v>574</v>
       </c>
       <c r="Q7" t="n">
-        <v>1550</v>
+        <v>1306</v>
       </c>
       <c r="R7" t="n">
-        <v>3098</v>
+        <v>1880</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38782467</t>
+          <t>1206099126</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38782467</t>
+          <t>https://m.place.naver.com/place/1206099126</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 헬스&amp;PT 작전점</t>
+          <t>스텔라 짐 여성전용 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>xforce_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1496-8948</t>
+          <t>0507-1382-1847</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 주부토로 372 금영프라자 5층 올나잇피트니스</t>
+          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sstella.gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1191,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wv1f</t>
+          <t>https://talk.naver.com/ct/w1qa97p</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>641</v>
+        <v>309</v>
       </c>
       <c r="Q8" t="n">
-        <v>634</v>
+        <v>220</v>
       </c>
       <c r="R8" t="n">
-        <v>1275</v>
+        <v>529</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1294236033</t>
+          <t>1938830886</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1294236033</t>
+          <t>https://m.place.naver.com/place/1938830886</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>ironfitnesssamsan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1483-2126</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천 부평구 부평북로 448 로얄프라자 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ironfitnesssamsan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,12 +1282,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46104</t>
+          <t>https://talk.naver.com/ct/w451o2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1243</v>
+        <v>707</v>
       </c>
       <c r="Q9" t="n">
-        <v>1242</v>
+        <v>291</v>
       </c>
       <c r="R9" t="n">
-        <v>2485</v>
+        <v>998</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1098353648</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1098353648</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오빠네헬스장&amp;PT 부평점</t>
+          <t>이룸휘트니스&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>oppagym@naver.com</t>
+          <t>eroom_fitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1361-1167</t>
+          <t>0507-1389-9940</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 부평구 부흥로 265 501호</t>
+          <t>인천 남동구 호구포로 887 하나프라자 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oppagym</t>
+          <t>https://blog.naver.com/eroom_fitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1397,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>768</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="n">
-        <v>2420</v>
+        <v>648</v>
       </c>
       <c r="R10" t="n">
-        <v>3188</v>
+        <v>762</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1538103381</t>
+          <t>1892216586</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538103381</t>
+          <t>https://m.place.naver.com/place/1892216586</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인싸짐 계산점 헬스 PT</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mukiwihaeundoung@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-3818</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 계양구 계양대로 147 부평농협 교대역지점 2층</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inssagym_pay?igsh=Zzgya21hNGR3N3g3</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1476,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>751</v>
+        <v>1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>2480</v>
+        <v>931</v>
       </c>
       <c r="R11" t="n">
-        <v>3231</v>
+        <v>2313</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,989 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1524298359</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1524298359</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>클래식더짐 PT&amp;헬스</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>happy3747@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1368-4594</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 신송로125번길 7 이리옴프라자 5층 505호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/happy3747</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>555</v>
-      </c>
-      <c r="R12" t="n">
-        <v>634</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1148859143</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1148859143</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>힙디자인팩토리 PT 검단 신도시점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>natural_sehun@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1384-6150</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>인천광역시 서구 이음대로 459 파라곤프라자 3층 힙디자인팩토리</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47sit</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1723</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1707</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3430</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1945940640</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1945940640</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>더피티짐 프리미엄 학원가점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>qoqofh677@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1446-9681</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://theptgym.clickn.co.kr/</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1808</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1816</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3624</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1063156519</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>프롬바디PT&amp;필라테스 인천대입구역점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>yoonse1995@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1425-0923</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 324호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://frombody.kr</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ofx5</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1538</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1543</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3081</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1472986584</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1472986584</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>샤머니짐 송도점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>resort_6@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1330-9030</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 컨벤시아대로 81 드림시티 7층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>920</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>920</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1840</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1040543457</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 송도점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1356-5739</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 하모니로 158 송도타임스페이스 B동 7층 702호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wual9v3</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>444</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>449</v>
-      </c>
-      <c r="R17" t="n">
-        <v>893</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2019067639</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2019067639</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>구월동PT 시크릿짐</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>secret_gym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1380-1228</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>인천광역시 남동구 용천로 80 201호,203호 시크릿짐</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4luwu</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2329</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2334</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4663</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>34698775</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/34698775</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>여성전용PT 핏투핏 송도점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>waterfallbody@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1458-9510</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 아트센터대로 87 401동 2층 210호</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wdg5hky</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>775</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>779</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1554</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1851119903</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1851119903</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>피지컬랩 송도PT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>maxyh7@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1332-2194</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>인천광역시 연수구 테크노파크로111번길 11 시카고 타워 502호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4umh7</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>546</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>546</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1092</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1826127652</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1826127652</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>올나잇 피트니스 부평점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>all_night_b@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1334-5596</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>인천광역시 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/all.night_official</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1306</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1177</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2483</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1342318850</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/인천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/인천_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,44 +559,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>테이스트피트니스헬스&amp;PT24시 인천호구포역점</t>
+          <t>스텔라 짐 여성전용 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tastehgp@naver.com</t>
+          <t>xforce_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1313-9022</t>
+          <t>0507-1382-1847</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 남동구 호구포로 212 4층 401호 402호, 403호</t>
+          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_exmwzX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4a1vf2</t>
+          <t>https://talk.naver.com/ct/w1qa97p</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>48</v>
+        <v>309</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="R2" t="n">
-        <v>69</v>
+        <v>529</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2089899080</t>
+          <t>1938830886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2089899080</t>
+          <t>https://m.place.naver.com/place/1938830886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>머슬몽키짐</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>coke3183@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1407-9979</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muscle_monkey_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4btcu</t>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>234</v>
+        <v>656</v>
       </c>
       <c r="Q3" t="n">
-        <v>147</v>
+        <v>869</v>
       </c>
       <c r="R3" t="n">
-        <v>381</v>
+        <v>1525</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>38234040</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38234040</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
+          <t>https://talk.naver.com/ct/webpfty</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>656</v>
+        <v>1899</v>
       </c>
       <c r="Q4" t="n">
-        <v>859</v>
+        <v>953</v>
       </c>
       <c r="R4" t="n">
-        <v>1515</v>
+        <v>2852</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle.gym02</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/webpfty</t>
+          <t>https://talk.naver.com/ct/w4aher</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1893</v>
+        <v>1315</v>
       </c>
       <c r="Q5" t="n">
-        <v>949</v>
+        <v>3057</v>
       </c>
       <c r="R5" t="n">
-        <v>2842</v>
+        <v>4372</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올나잇 피트니스 부평점</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>all_night_b@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1334-5596</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 경원대로1403번길 33 뉴월드프라자 11층 올나잇 피트니스 부평점</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/all.night_official</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41wqc</t>
+          <t>https://talk.naver.com/ct/w5xn31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1308</v>
+        <v>1021</v>
       </c>
       <c r="Q6" t="n">
-        <v>920</v>
+        <v>324</v>
       </c>
       <c r="R6" t="n">
-        <v>2228</v>
+        <v>1345</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1342318850</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342318850</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>매드볼릭 PT 헬스장 송도</t>
+          <t>샌드짐 계산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>madbolic-songdo@naver.com</t>
+          <t>sandgym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1352-6741</t>
+          <t>0507-1370-2771</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 연수구 테크노파크로111번길 11 시카고타워 6층</t>
+          <t>인천 계양구 경명대로 1063 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madbolic-songdo</t>
+          <t>https://blog.naver.com/sandgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46104</t>
+          <t>https://talk.naver.com/ct/w5xnta</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="Q7" t="n">
-        <v>1306</v>
+        <v>1157</v>
       </c>
       <c r="R7" t="n">
-        <v>1880</v>
+        <v>1761</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1206099126</t>
+          <t>1722099342</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206099126</t>
+          <t>https://m.place.naver.com/place/1722099342</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스텔라 짐 여성전용 헬스PT</t>
+          <t>피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>xforce_@naver.com</t>
+          <t>lfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1382-1847</t>
+          <t>0507-1441-2226</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
+          <t>인천 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sstella.gym</t>
+          <t>http://www.fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1qa97p</t>
+          <t>https://talk.naver.com/ct/w4um0j</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>309</v>
+        <v>2777</v>
       </c>
       <c r="Q8" t="n">
-        <v>220</v>
+        <v>377</v>
       </c>
       <c r="R8" t="n">
-        <v>529</v>
+        <v>3154</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1938830886</t>
+          <t>1562966214</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1938830886</t>
+          <t>https://m.place.naver.com/place/1562966214</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아이언휘트니스 헬스&amp;PT 삼산점</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ironfitnesssamsan@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1483-2126</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 부평구 부평북로 448 로얄프라자 2층</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ironfitnesssamsan</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w451o2</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>707</v>
+        <v>1386</v>
       </c>
       <c r="Q9" t="n">
-        <v>291</v>
+        <v>933</v>
       </c>
       <c r="R9" t="n">
-        <v>998</v>
+        <v>2319</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,56 +1326,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1098353648</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098353648</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이룸휘트니스&amp;필라테스</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eroom_fitness@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1389-9940</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 남동구 호구포로 887 하나프라자 3층</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eroom_fitness</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,15 +1385,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>114</v>
+        <v>317</v>
       </c>
       <c r="Q10" t="n">
-        <v>648</v>
+        <v>1924</v>
       </c>
       <c r="R10" t="n">
-        <v>762</v>
+        <v>2241</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1892216586</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892216586</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>바름핏 PT&amp;필라테스 본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>brfpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1455-8691</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 미추홀구 소성로 150 2층바름핏</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/w4yrsh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1382</v>
+        <v>287</v>
       </c>
       <c r="Q11" t="n">
-        <v>931</v>
+        <v>375</v>
       </c>
       <c r="R11" t="n">
-        <v>2313</v>
+        <v>662</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1493566392</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1493566392</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/인천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/인천_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,44 +559,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스텔라 짐 여성전용 헬스PT</t>
+          <t>테이스트피트니스헬스&amp;PT24시 인천호구포역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>xforce_@naver.com</t>
+          <t>tastehgp@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1382-1847</t>
+          <t>0507-1313-9022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
+          <t>인천 남동구 호구포로 212 4층 401호 402호, 403호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_exmwzX</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w1qa97p</t>
+          <t>https://talk.naver.com/ct/w4a1vf2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>309</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="n">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="R2" t="n">
-        <v>529</v>
+        <v>71</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1938830886</t>
+          <t>2089899080</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1938830886</t>
+          <t>https://m.place.naver.com/place/2089899080</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>터닝포인트짐 헬스 PT 가좌점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>turningpointgym_gajw@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>032-576-1365</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 서구 원적로 85 우신프라자 B1층 B01~B02호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/turningpointgym_gajw</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
+          <t>https://talk.naver.com/ct/w4oq2u</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>656</v>
+        <v>538</v>
       </c>
       <c r="Q3" t="n">
-        <v>869</v>
+        <v>1548</v>
       </c>
       <c r="R3" t="n">
-        <v>1525</v>
+        <v>2086</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>1588426455</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/1588426455</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle.gym02</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/webpfty</t>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1899</v>
+        <v>656</v>
       </c>
       <c r="Q4" t="n">
-        <v>953</v>
+        <v>872</v>
       </c>
       <c r="R4" t="n">
-        <v>2852</v>
+        <v>1528</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 부평역점</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany86@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1339-9618</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4aher</t>
+          <t>https://talk.naver.com/ct/webpfty</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1315</v>
+        <v>1899</v>
       </c>
       <c r="Q5" t="n">
-        <v>3057</v>
+        <v>953</v>
       </c>
       <c r="R5" t="n">
-        <v>4372</v>
+        <v>2852</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1118966019</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118966019</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>카우짐24시 서구청역점</t>
+          <t>스포애니 부평역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>coco951215@naver.com</t>
+          <t>spoany86@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1376-7926</t>
+          <t>0507-1339-9618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
+          <t>인천 부평구 시장로 7 MH타워 B1 스포애니부평역점</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/cowgymseogu</t>
+          <t>https://blog.naver.com/spoany86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xn31</t>
+          <t>https://talk.naver.com/ct/w4aher</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1021</v>
+        <v>1315</v>
       </c>
       <c r="Q6" t="n">
-        <v>324</v>
+        <v>3057</v>
       </c>
       <c r="R6" t="n">
-        <v>1345</v>
+        <v>4372</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1106839652</t>
+          <t>1118966019</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1106839652</t>
+          <t>https://m.place.naver.com/place/1118966019</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>샌드짐 계산점</t>
+          <t>스텔라 짐 여성전용 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sandgym@naver.com</t>
+          <t>xforce_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1370-2771</t>
+          <t>0507-1382-1847</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 계양구 경명대로 1063 3층</t>
+          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sandgym</t>
+          <t>https://www.instagram.com/sstella.gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xnta</t>
+          <t>https://talk.naver.com/ct/w1qa97p</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>604</v>
+        <v>309</v>
       </c>
       <c r="Q7" t="n">
-        <v>1157</v>
+        <v>220</v>
       </c>
       <c r="R7" t="n">
-        <v>1761</v>
+        <v>529</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1722099342</t>
+          <t>1938830886</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722099342</t>
+          <t>https://m.place.naver.com/place/1938830886</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스 연구소 인하대역점</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1441-2226</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.fitnessinstitute.co.kr/</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4um0j</t>
+          <t>https://talk.naver.com/ct/w5xn31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2777</v>
+        <v>1021</v>
       </c>
       <c r="Q8" t="n">
-        <v>377</v>
+        <v>324</v>
       </c>
       <c r="R8" t="n">
-        <v>3154</v>
+        <v>1345</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1562966214</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562966214</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,39 +1245,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>lfitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1441-2226</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>http://www.fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/w4um0j</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1386</v>
+        <v>2777</v>
       </c>
       <c r="Q9" t="n">
-        <v>933</v>
+        <v>377</v>
       </c>
       <c r="R9" t="n">
-        <v>2319</v>
+        <v>3154</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1562966214</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1562966214</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>무포스 PT FT 송도점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>moveforstrength@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1406-4500</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 연수구 인천타워대로197번길 16 2층 226호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://www.moveforstrength.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
+          <t>https://talk.naver.com/ct/w5x24z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>317</v>
+        <v>115</v>
       </c>
       <c r="Q10" t="n">
-        <v>1924</v>
+        <v>644</v>
       </c>
       <c r="R10" t="n">
-        <v>2241</v>
+        <v>759</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1426191152</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1426191152</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>바름핏 PT&amp;필라테스 본점</t>
+          <t>여성전용PT복숭아헬스장</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>brfpt@naver.com</t>
+          <t>52997994@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1455-8691</t>
+          <t>0507-1417-8063</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 미추홀구 소성로 150 2층바름핏</t>
+          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com//@복숭아헬스장</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4yrsh</t>
+          <t>https://talk.naver.com/ct/wit7sbd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>287</v>
+        <v>125</v>
       </c>
       <c r="Q11" t="n">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="R11" t="n">
-        <v>662</v>
+        <v>462</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,15 +1522,211 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1493566392</t>
+          <t>2040870567</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493566392</t>
+          <t>https://m.place.naver.com/place/2040870567</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>샤머니짐 송도점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>shamanigym_songdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1330-9030</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shamanigym/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1386</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>933</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2319</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1040543457</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1040543457</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>더피티짐 프리미엄 학원가점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>qoqofh677@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1446-9681</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://theptgym.clickn.co.kr/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4mk22</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>317</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1924</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2241</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1063156519</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1063156519</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/인천_헬스장.xlsx
+++ b/naver-place-crawler/results_health/인천_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>임팩트짐 검암점</t>
+          <t>스텔라 짐 여성전용 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>znzl6268@naver.com</t>
+          <t>xforce_@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>032-230-9688</t>
+          <t>0507-1382-1847</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 서구 검암로30번길 20 2, 3층</t>
+          <t>인천 남동구 만수서로 62 제이제이스타프라자 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sstella.gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tlf4s</t>
+          <t>https://talk.naver.com/ct/w1qa97p</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>105</v>
+        <v>309</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="R2" t="n">
-        <v>132</v>
+        <v>529</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2012324353</t>
+          <t>1938830886</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2012324353</t>
+          <t>https://m.place.naver.com/place/1938830886</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +657,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>랜드짐 검단점</t>
+          <t>테이스트피트니스헬스&amp;PT24시 인천호구포역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dongle_1@naver.com</t>
+          <t>tastehgp@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1355-7937</t>
+          <t>0507-1313-9022</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 서구 완정로 172 6층</t>
+          <t>인천 남동구 호구포로 212 4층 401호 402호, 403호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://naver.me/GXg2CKrZ</t>
+          <t>http://pf.kakao.com/_exmwzX</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wllk3p7</t>
+          <t>https://talk.naver.com/ct/w4a1vf2</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="Q3" t="n">
-        <v>157</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>290</v>
+        <v>71</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074197372</t>
+          <t>2089899080</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074197372</t>
+          <t>https://m.place.naver.com/place/2089899080</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>커넥트짐 구월동 헬스&amp;PT</t>
+          <t>머슬몽키짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>connectgympro@naver.com</t>
+          <t>coke3183@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1382-1877</t>
+          <t>0507-1407-9979</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
+          <t>인천 연수구 청량로185번길 37 에스엠프라자 501,502호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/connectgym.pro</t>
+          <t>https://www.instagram.com/muscle_monkey_gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wz5kx6y</t>
+          <t>https://talk.naver.com/ct/w4btcu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>659</v>
+        <v>235</v>
       </c>
       <c r="Q4" t="n">
-        <v>876</v>
+        <v>147</v>
       </c>
       <c r="R4" t="n">
-        <v>1535</v>
+        <v>382</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1964930363</t>
+          <t>38234040</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1964930363</t>
+          <t>https://m.place.naver.com/place/38234040</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,34 +853,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
+          <t>커넥트짐 구월동 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>miraclebym02@naver.com</t>
+          <t>connectgympro@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1412-0034</t>
+          <t>0507-1382-1877</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
+          <t>인천 남동구 인주대로 593 엔타스빌딩 1층 커넥트짐 구월점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle.gym02</t>
+          <t>https://www.instagram.com/connectgym.pro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/webpfty</t>
+          <t>https://talk.naver.com/ct/wz5kx6y</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1899</v>
+        <v>659</v>
       </c>
       <c r="Q5" t="n">
-        <v>955</v>
+        <v>881</v>
       </c>
       <c r="R5" t="n">
-        <v>2854</v>
+        <v>1540</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>35823978</t>
+          <t>1964930363</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35823978</t>
+          <t>https://m.place.naver.com/place/1964930363</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 부평시장역점</t>
+          <t>미라클짐 삼산점 헬스 GX 필라테스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany_70@naver.com</t>
+          <t>miraclebym02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1428-9618</t>
+          <t>0507-1412-0034</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
+          <t>인천 부평구 길주로 643 거림타워 13층,14층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_70</t>
+          <t>https://www.instagram.com/miracle.gym02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w441cj</t>
+          <t>https://talk.naver.com/ct/webpfty</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1528</v>
+        <v>1901</v>
       </c>
       <c r="Q6" t="n">
-        <v>2039</v>
+        <v>955</v>
       </c>
       <c r="R6" t="n">
-        <v>3567</v>
+        <v>2856</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1163734622</t>
+          <t>35823978</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163734622</t>
+          <t>https://m.place.naver.com/place/35823978</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1049,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>여성전용PT복숭아헬스장</t>
+          <t>스포애니 부평시장역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52997994@naver.com</t>
+          <t>spoany_70@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-8063</t>
+          <t>0507-1428-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천 남동구 인주대로 588 대암빌딩 2층</t>
+          <t>인천 부평구 부평대로 83 강남타워 9, 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com//@복숭아헬스장</t>
+          <t>https://blog.naver.com/spoany_70</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wit7sbd</t>
+          <t>https://talk.naver.com/ct/w441cj</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>125</v>
+        <v>1529</v>
       </c>
       <c r="Q7" t="n">
-        <v>352</v>
+        <v>2038</v>
       </c>
       <c r="R7" t="n">
-        <v>477</v>
+        <v>3567</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2040870567</t>
+          <t>1163734622</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040870567</t>
+          <t>https://m.place.naver.com/place/1163734622</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피트니스 연구소 부평산곡점 헬스PT</t>
+          <t>카우짐24시 서구청역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lfitness5@naver.com</t>
+          <t>coco951215@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-2251</t>
+          <t>0507-1376-7926</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천 부평구 원적로 295 더 루츠 스퀘어 5층</t>
+          <t>인천 서구 탁옥로51번길 11 702호, 703호, 704호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://fitnessinstitute.co.kr/</t>
+          <t>https://link.inpock.co.kr/cowgymseogu</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40cxc</t>
+          <t>https://talk.naver.com/ct/w5xn31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>986</v>
+        <v>1020</v>
       </c>
       <c r="Q8" t="n">
-        <v>493</v>
+        <v>324</v>
       </c>
       <c r="R8" t="n">
-        <v>1479</v>
+        <v>1344</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1338376061</t>
+          <t>1106839652</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338376061</t>
+          <t>https://m.place.naver.com/place/1106839652</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바디플라워 계양구청점 헬스 PT 재활 체형교정</t>
+          <t>샤머니짐 송도점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyflower@naver.com</t>
+          <t>shamanigym_songdo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1312-9682</t>
+          <t>0507-1330-9030</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천 계양구 계산새로87번길 6 레드몰 2차 4층</t>
+          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyflower</t>
+          <t>https://www.instagram.com/shamanigym/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4hit</t>
+          <t>https://talk.naver.com/ct/w7ng6u3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>109</v>
+        <v>1386</v>
       </c>
       <c r="Q9" t="n">
-        <v>843</v>
+        <v>938</v>
       </c>
       <c r="R9" t="n">
-        <v>952</v>
+        <v>2324</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>933633163</t>
+          <t>1040543457</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/933633163</t>
+          <t>https://m.place.naver.com/place/1040543457</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>샤머니짐 송도점</t>
+          <t>더피티짐 프리미엄 학원가점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>shamanigym_songdo@naver.com</t>
+          <t>qoqofh677@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1330-9030</t>
+          <t>0507-1446-9681</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천 연수구 컨벤시아대로 81 드림시티 7층</t>
+          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shamanigym/</t>
+          <t>https://theptgym.clickn.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ng6u3</t>
+          <t>https://talk.naver.com/ct/w4mk22</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1386</v>
+        <v>317</v>
       </c>
       <c r="Q10" t="n">
-        <v>936</v>
+        <v>1938</v>
       </c>
       <c r="R10" t="n">
-        <v>2322</v>
+        <v>2255</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1040543457</t>
+          <t>1063156519</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040543457</t>
+          <t>https://m.place.naver.com/place/1063156519</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,34 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>더피티짐 프리미엄 학원가점</t>
+          <t>더피티짐 프리미엄 루원시티점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>qoqofh677@naver.com</t>
+          <t>gktk1877@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1446-9681</t>
+          <t>0507-1375-9681</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 연수구 해돋이로 160-19 카리스프라자 3층 301호</t>
+          <t>인천 서구 봉오대로 270 302동 상가B 110~112호 (파리바게트 위층)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://theptgym.clickn.co.kr/</t>
+          <t>https://blog.naver.com/gktk1877</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mk22</t>
+          <t>https://talk.naver.com/ct/w5wpot</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>317</v>
+        <v>121</v>
       </c>
       <c r="Q11" t="n">
-        <v>1935</v>
+        <v>179</v>
       </c>
       <c r="R11" t="n">
-        <v>2252</v>
+        <v>300</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1063156519</t>
+          <t>1650465158</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1063156519</t>
+          <t>https://m.place.naver.com/place/1650465158</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
